--- a/docs/testbirthdays.xlsx
+++ b/docs/testbirthdays.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_EB45A67B026F236B240BE4472FA54CAF4993320B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20D3E7F4-B569-4395-87B3-3D33D660B538}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_EB45A67B026F236B240BE4472FA54CAF4993320B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAC9B554-C7AA-4A5C-8363-A1AB78C111AA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
     <t>Bob Jr</t>
   </si>
   <si>
-    <t>No news</t>
+    <t>No News</t>
   </si>
 </sst>
 </file>

--- a/docs/testbirthdays.xlsx
+++ b/docs/testbirthdays.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_EB45A67B026F236B240BE4472FA54CAF4993320B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAC9B554-C7AA-4A5C-8363-A1AB78C111AA}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_EB45A67B026F236B240BE4472FA54CAF4993320B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F084212A-F055-42F1-8081-B5712C1B5B62}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,7 +507,7 @@
         <v>46233</v>
       </c>
       <c r="C4" s="1">
-        <v>45487</v>
+        <v>45518</v>
       </c>
     </row>
   </sheetData>

--- a/docs/testbirthdays.xlsx
+++ b/docs/testbirthdays.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_EB45A67B026F236B240BE4472FA54CAF4993320B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F084212A-F055-42F1-8081-B5712C1B5B62}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_EB45A67B026F236B240BE4472FA54CAF4993320B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A621A4D-EB40-47EE-A315-9E34525B51EF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Name</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>No News</t>
+  </si>
+  <si>
+    <t>Kevin</t>
   </si>
 </sst>
 </file>
@@ -90,9 +93,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,11 +436,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.26953125" customWidth="1"/>
-    <col min="2" max="3" width="10.1796875" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.54296875" customWidth="1"/>
     <col min="5" max="6" width="10.1796875" customWidth="1"/>
     <col min="7" max="7" width="9.26953125" customWidth="1"/>
@@ -510,6 +515,17 @@
         <v>45518</v>
       </c>
     </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2">
+        <v>36980</v>
+      </c>
+      <c r="C5" s="2">
+        <v>45521</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/docs/testbirthdays.xlsx
+++ b/docs/testbirthdays.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_EB45A67B026F236B240BE4472FA54CAF4993320B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A621A4D-EB40-47EE-A315-9E34525B51EF}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_EB45A67B026F236B240BE4472FA54CAF4993320B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3D0B6EF-6FE9-4170-BAC3-4D42557A012A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Name</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Kevin</t>
+  </si>
+  <si>
+    <t>Safety Notice</t>
   </si>
 </sst>
 </file>
@@ -436,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.26953125" customWidth="1"/>
@@ -450,7 +453,7 @@
     <col min="10" max="24" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -472,8 +475,11 @@
       <c r="I1" t="s">
         <v>6</v>
       </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -493,7 +499,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -504,7 +510,7 @@
         <v>44391</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -515,7 +521,7 @@
         <v>45518</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>12</v>
       </c>
